--- a/EEE3096S SMTROS022 Pracs/Prac 3/Misc/Raw Data.xlsx
+++ b/EEE3096S SMTROS022 Pracs/Prac 3/Misc/Raw Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uctcloud-my.sharepoint.com/personal/smtros022_myuct_ac_za/Documents/Fourth Year/Sem 2/EEE3096S/EEE3096S Git Repo SMTROS022/EEE3096S SMTROS022 Pracs/Prac 3/Misc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{C64EA8E1-BEFA-49D1-BF1E-9A3345DDF2F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44CA6F7B-6711-4A77-BC51-BECC1736D54F}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="8_{C64EA8E1-BEFA-49D1-BF1E-9A3345DDF2F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CBF68F7-43B0-4D0F-8A88-F4B94C2AF643}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DB21F44C-0F24-4ECD-93E7-EFB15482C059}"/>
   </bookViews>
@@ -1039,12 +1039,24 @@
       <c r="M12" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
+      <c r="N12" s="4">
+        <v>429346</v>
+      </c>
+      <c r="O12" s="4">
+        <v>21874</v>
+      </c>
+      <c r="P12" s="4">
+        <v>968024</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>48764</v>
+      </c>
+      <c r="R12" s="4">
+        <v>1858360</v>
+      </c>
+      <c r="S12" s="4">
+        <v>93198</v>
+      </c>
       <c r="T12" s="4"/>
       <c r="U12" s="4"/>
       <c r="V12" s="4"/>
@@ -1087,12 +1099,24 @@
       <c r="M13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="6"/>
-      <c r="S13" s="6"/>
+      <c r="N13" s="6">
+        <v>669809</v>
+      </c>
+      <c r="O13" s="6">
+        <v>34169</v>
+      </c>
+      <c r="P13" s="6">
+        <v>1510353</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>76225</v>
+      </c>
+      <c r="R13" s="6">
+        <v>2899477</v>
+      </c>
+      <c r="S13" s="6">
+        <v>145712</v>
+      </c>
       <c r="T13" s="6"/>
       <c r="U13" s="6"/>
       <c r="V13" s="6"/>
@@ -1135,12 +1159,24 @@
       <c r="M14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="4"/>
-      <c r="S14" s="4"/>
+      <c r="N14" s="4">
+        <v>966227</v>
+      </c>
+      <c r="O14" s="4">
+        <v>49327</v>
+      </c>
+      <c r="P14" s="4">
+        <v>2180459</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>110117</v>
+      </c>
+      <c r="R14" s="4">
+        <v>4184222</v>
+      </c>
+      <c r="S14" s="4">
+        <v>210418</v>
+      </c>
       <c r="T14" s="4"/>
       <c r="U14" s="4"/>
       <c r="V14" s="4"/>
@@ -1183,10 +1219,18 @@
       <c r="M15" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
-      <c r="Q15" s="6"/>
+      <c r="N15" s="6">
+        <v>1315085</v>
+      </c>
+      <c r="O15" s="6">
+        <v>67163</v>
+      </c>
+      <c r="P15" s="6">
+        <v>2963856</v>
+      </c>
+      <c r="Q15" s="6">
+        <v>149757</v>
+      </c>
       <c r="R15" s="6"/>
       <c r="S15" s="6"/>
       <c r="T15" s="6"/>
@@ -1231,10 +1275,18 @@
       <c r="M16" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N16" s="4"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="4"/>
-      <c r="Q16" s="4"/>
+      <c r="N16" s="4">
+        <v>1715815</v>
+      </c>
+      <c r="O16" s="4">
+        <v>87696</v>
+      </c>
+      <c r="P16" s="4">
+        <v>3873054</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>195829</v>
+      </c>
       <c r="R16" s="4"/>
       <c r="S16" s="4"/>
       <c r="T16" s="4"/>

--- a/EEE3096S SMTROS022 Pracs/Prac 3/Misc/Raw Data.xlsx
+++ b/EEE3096S SMTROS022 Pracs/Prac 3/Misc/Raw Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uctcloud-my.sharepoint.com/personal/smtros022_myuct_ac_za/Documents/Fourth Year/Sem 2/EEE3096S/EEE3096S Git Repo SMTROS022/EEE3096S SMTROS022 Pracs/Prac 3/Misc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="8_{C64EA8E1-BEFA-49D1-BF1E-9A3345DDF2F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CBF68F7-43B0-4D0F-8A88-F4B94C2AF643}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="8_{C64EA8E1-BEFA-49D1-BF1E-9A3345DDF2F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C613415-518B-4512-A505-4969D2B4FC91}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DB21F44C-0F24-4ECD-93E7-EFB15482C059}"/>
   </bookViews>
@@ -1057,8 +1057,12 @@
       <c r="S12" s="4">
         <v>93198</v>
       </c>
-      <c r="T12" s="4"/>
-      <c r="U12" s="4"/>
+      <c r="T12" s="4">
+        <v>2745724</v>
+      </c>
+      <c r="U12" s="4">
+        <v>137482</v>
+      </c>
       <c r="V12" s="4"/>
       <c r="W12" s="4"/>
     </row>
@@ -1117,8 +1121,12 @@
       <c r="S13" s="6">
         <v>145712</v>
       </c>
-      <c r="T13" s="6"/>
-      <c r="U13" s="6"/>
+      <c r="T13" s="6">
+        <v>4281267</v>
+      </c>
+      <c r="U13" s="6">
+        <v>214830</v>
+      </c>
       <c r="V13" s="6"/>
       <c r="W13" s="6"/>
     </row>
@@ -1177,8 +1185,12 @@
       <c r="S14" s="4">
         <v>210418</v>
       </c>
-      <c r="T14" s="4"/>
-      <c r="U14" s="4"/>
+      <c r="T14" s="4">
+        <v>6180826</v>
+      </c>
+      <c r="U14" s="4">
+        <v>310353</v>
+      </c>
       <c r="V14" s="4"/>
       <c r="W14" s="4"/>
     </row>
@@ -1231,10 +1243,18 @@
       <c r="Q15" s="6">
         <v>149757</v>
       </c>
-      <c r="R15" s="6"/>
-      <c r="S15" s="6"/>
-      <c r="T15" s="6"/>
-      <c r="U15" s="6"/>
+      <c r="R15" s="6">
+        <v>5685832</v>
+      </c>
+      <c r="S15" s="6">
+        <v>286090</v>
+      </c>
+      <c r="T15" s="6">
+        <v>8399750</v>
+      </c>
+      <c r="U15" s="6">
+        <v>422011</v>
+      </c>
       <c r="V15" s="6"/>
       <c r="W15" s="6"/>
     </row>
@@ -1287,10 +1307,18 @@
       <c r="Q16" s="4">
         <v>195829</v>
       </c>
-      <c r="R16" s="4"/>
-      <c r="S16" s="4"/>
-      <c r="T16" s="4"/>
-      <c r="U16" s="4"/>
+      <c r="R16" s="4">
+        <v>7434783</v>
+      </c>
+      <c r="S16" s="4">
+        <v>374326</v>
+      </c>
+      <c r="T16" s="4">
+        <v>10985970</v>
+      </c>
+      <c r="U16" s="4">
+        <v>552290</v>
+      </c>
       <c r="V16" s="4"/>
       <c r="W16" s="4"/>
     </row>

--- a/EEE3096S SMTROS022 Pracs/Prac 3/Misc/Raw Data.xlsx
+++ b/EEE3096S SMTROS022 Pracs/Prac 3/Misc/Raw Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uctcloud-my.sharepoint.com/personal/smtros022_myuct_ac_za/Documents/Fourth Year/Sem 2/EEE3096S/EEE3096S Git Repo SMTROS022/EEE3096S SMTROS022 Pracs/Prac 3/Misc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="8_{C64EA8E1-BEFA-49D1-BF1E-9A3345DDF2F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C613415-518B-4512-A505-4969D2B4FC91}"/>
+  <xr:revisionPtr revIDLastSave="118" documentId="8_{C64EA8E1-BEFA-49D1-BF1E-9A3345DDF2F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{387BA547-A2C0-4A0E-8513-80FE10D339B1}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DB21F44C-0F24-4ECD-93E7-EFB15482C059}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="24">
   <si>
     <t>Resolution</t>
   </si>
@@ -87,6 +87,27 @@
   </si>
   <si>
     <t>Task 2 F0</t>
+  </si>
+  <si>
+    <t>CPU Cycles</t>
+  </si>
+  <si>
+    <t>Throughput</t>
+  </si>
+  <si>
+    <t>749.01709</t>
+  </si>
+  <si>
+    <t>749.217102</t>
+  </si>
+  <si>
+    <t>747.339172</t>
+  </si>
+  <si>
+    <t>747.078003</t>
+  </si>
+  <si>
+    <t>747.308899</t>
   </si>
 </sst>
 </file>
@@ -586,17 +607,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D06E983-B581-4B51-A88B-00887F6C9E77}">
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
-    <col min="2" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="15" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.42578125" customWidth="1"/>
+    <col min="12" max="12" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -1063,8 +1088,12 @@
       <c r="U12" s="4">
         <v>137482</v>
       </c>
-      <c r="V12" s="4"/>
-      <c r="W12" s="4"/>
+      <c r="V12" s="4">
+        <v>3631724</v>
+      </c>
+      <c r="W12" s="4">
+        <v>181695</v>
+      </c>
     </row>
     <row r="13" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
@@ -1127,8 +1156,12 @@
       <c r="U13" s="6">
         <v>214830</v>
       </c>
-      <c r="V13" s="6"/>
-      <c r="W13" s="6"/>
+      <c r="V13" s="6">
+        <v>5660801</v>
+      </c>
+      <c r="W13" s="6">
+        <v>283834</v>
+      </c>
     </row>
     <row r="14" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
@@ -1191,8 +1224,12 @@
       <c r="U14" s="4">
         <v>310353</v>
       </c>
-      <c r="V14" s="4"/>
-      <c r="W14" s="4"/>
+      <c r="V14" s="4">
+        <v>8174642</v>
+      </c>
+      <c r="W14" s="4">
+        <v>410146</v>
+      </c>
     </row>
     <row r="15" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
@@ -1255,8 +1292,12 @@
       <c r="U15" s="6">
         <v>422011</v>
       </c>
-      <c r="V15" s="6"/>
-      <c r="W15" s="6"/>
+      <c r="V15" s="6">
+        <v>11110549</v>
+      </c>
+      <c r="W15" s="6">
+        <v>557772</v>
+      </c>
     </row>
     <row r="16" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
@@ -1319,8 +1360,192 @@
       <c r="U16" s="4">
         <v>552290</v>
       </c>
-      <c r="V16" s="4"/>
-      <c r="W16" s="4"/>
+      <c r="V16" s="4">
+        <v>14531940</v>
+      </c>
+      <c r="W16" s="4">
+        <v>729987</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="4">
+        <v>429346</v>
+      </c>
+      <c r="C20" s="4">
+        <v>1456</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="H20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I20" s="4">
+        <v>429346</v>
+      </c>
+      <c r="J20" s="4">
+        <v>21874</v>
+      </c>
+      <c r="K20" s="4">
+        <v>1049952000</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="6">
+        <v>669809</v>
+      </c>
+      <c r="C21" s="6">
+        <v>2272</v>
+      </c>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="H21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="6">
+        <v>669809</v>
+      </c>
+      <c r="J21" s="6">
+        <v>34169</v>
+      </c>
+      <c r="K21" s="6">
+        <v>1640112000</v>
+      </c>
+      <c r="L21" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="4">
+        <v>966227</v>
+      </c>
+      <c r="C22" s="4">
+        <v>3278</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="H22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I22" s="4">
+        <v>966227</v>
+      </c>
+      <c r="J22" s="4">
+        <v>49327</v>
+      </c>
+      <c r="K22" s="4">
+        <v>2367696000</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="6">
+        <v>1315085</v>
+      </c>
+      <c r="C23" s="6">
+        <v>4462</v>
+      </c>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="H23" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="I23" s="6">
+        <v>1315085</v>
+      </c>
+      <c r="J23" s="6">
+        <v>67163</v>
+      </c>
+      <c r="K23" s="6">
+        <v>3223824000</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="4">
+        <v>1715815</v>
+      </c>
+      <c r="C24" s="4">
+        <v>5822</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="H24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I24" s="4">
+        <v>1715815</v>
+      </c>
+      <c r="J24" s="4">
+        <v>87696</v>
+      </c>
+      <c r="K24" s="4">
+        <v>4209408000</v>
+      </c>
+      <c r="L24" s="4" t="s">
+        <v>23</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="10">

--- a/EEE3096S SMTROS022 Pracs/Prac 3/Misc/Raw Data.xlsx
+++ b/EEE3096S SMTROS022 Pracs/Prac 3/Misc/Raw Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uctcloud-my.sharepoint.com/personal/smtros022_myuct_ac_za/Documents/Fourth Year/Sem 2/EEE3096S/EEE3096S Git Repo SMTROS022/EEE3096S SMTROS022 Pracs/Prac 3/Misc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="118" documentId="8_{C64EA8E1-BEFA-49D1-BF1E-9A3345DDF2F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{387BA547-A2C0-4A0E-8513-80FE10D339B1}"/>
+  <xr:revisionPtr revIDLastSave="132" documentId="8_{C64EA8E1-BEFA-49D1-BF1E-9A3345DDF2F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE692FE3-330D-483C-AA1A-1DD9B98B2E7B}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DB21F44C-0F24-4ECD-93E7-EFB15482C059}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="31">
   <si>
     <t>Resolution</t>
   </si>
@@ -108,6 +108,27 @@
   </si>
   <si>
     <t>747.308899</t>
+  </si>
+  <si>
+    <t>11248.1934</t>
+  </si>
+  <si>
+    <t>11263.9375</t>
+  </si>
+  <si>
+    <t>11243.1982</t>
+  </si>
+  <si>
+    <t>11243.0596</t>
+  </si>
+  <si>
+    <t>11254.917</t>
+  </si>
+  <si>
+    <t>Task 3 F4</t>
+  </si>
+  <si>
+    <t>Task 3 F0</t>
   </si>
 </sst>
 </file>
@@ -1369,10 +1390,10 @@
     </row>
     <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="H18" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -1417,8 +1438,12 @@
       <c r="C20" s="4">
         <v>1456</v>
       </c>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
+      <c r="D20" s="4">
+        <v>174790741</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>24</v>
+      </c>
       <c r="H20" s="3" t="s">
         <v>7</v>
       </c>
@@ -1445,8 +1470,12 @@
       <c r="C21" s="6">
         <v>2272</v>
       </c>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
+      <c r="D21" s="6">
+        <v>272728812</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>25</v>
+      </c>
       <c r="H21" s="5" t="s">
         <v>8</v>
       </c>
@@ -1473,8 +1502,12 @@
       <c r="C22" s="4">
         <v>3278</v>
       </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
+      <c r="D22" s="4">
+        <v>393453876</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="H22" s="3" t="s">
         <v>9</v>
       </c>
@@ -1501,8 +1534,12 @@
       <c r="C23" s="6">
         <v>4462</v>
       </c>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
+      <c r="D23" s="6">
+        <v>535541064</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>27</v>
+      </c>
       <c r="H23" s="5" t="s">
         <v>10</v>
       </c>
@@ -1529,8 +1566,12 @@
       <c r="C24" s="4">
         <v>5822</v>
       </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
+      <c r="D24" s="4">
+        <v>698745311</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>28</v>
+      </c>
       <c r="H24" s="3" t="s">
         <v>11</v>
       </c>

--- a/EEE3096S SMTROS022 Pracs/Prac 3/Misc/Raw Data.xlsx
+++ b/EEE3096S SMTROS022 Pracs/Prac 3/Misc/Raw Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uctcloud-my.sharepoint.com/personal/smtros022_myuct_ac_za/Documents/Fourth Year/Sem 2/EEE3096S/EEE3096S Git Repo SMTROS022/EEE3096S SMTROS022 Pracs/Prac 3/Misc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="132" documentId="8_{C64EA8E1-BEFA-49D1-BF1E-9A3345DDF2F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE692FE3-330D-483C-AA1A-1DD9B98B2E7B}"/>
+  <xr:revisionPtr revIDLastSave="409" documentId="8_{C64EA8E1-BEFA-49D1-BF1E-9A3345DDF2F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC05B23D-85A6-4021-B907-02E0DCE0A662}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DB21F44C-0F24-4ECD-93E7-EFB15482C059}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DB21F44C-0F24-4ECD-93E7-EFB15482C059}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="64">
   <si>
     <t>Resolution</t>
   </si>
@@ -129,13 +129,112 @@
   </si>
   <si>
     <t>Task 3 F0</t>
+  </si>
+  <si>
+    <t>Tile Count</t>
+  </si>
+  <si>
+    <t>320x240</t>
+  </si>
+  <si>
+    <t>480x270</t>
+  </si>
+  <si>
+    <t>640x320</t>
+  </si>
+  <si>
+    <t>800x450</t>
+  </si>
+  <si>
+    <t>1024x576</t>
+  </si>
+  <si>
+    <t>1280x720</t>
+  </si>
+  <si>
+    <t>1600x900</t>
+  </si>
+  <si>
+    <t>1920x1080</t>
+  </si>
+  <si>
+    <t>749.051331</t>
+  </si>
+  <si>
+    <t>747.300354</t>
+  </si>
+  <si>
+    <t>747.692688</t>
+  </si>
+  <si>
+    <t>747.366028</t>
+  </si>
+  <si>
+    <t>746.72821</t>
+  </si>
+  <si>
+    <t>747.357788</t>
+  </si>
+  <si>
+    <t>746.755371</t>
+  </si>
+  <si>
+    <t>746.572144</t>
+  </si>
+  <si>
+    <t>746.880981</t>
+  </si>
+  <si>
+    <t>746.601868</t>
+  </si>
+  <si>
+    <t>11248.6016</t>
+  </si>
+  <si>
+    <t>11247.7852</t>
+  </si>
+  <si>
+    <t>11251.2363</t>
+  </si>
+  <si>
+    <t>11249.3604</t>
+  </si>
+  <si>
+    <t>11249.4258</t>
+  </si>
+  <si>
+    <t>11259.375</t>
+  </si>
+  <si>
+    <t>35530.2812</t>
+  </si>
+  <si>
+    <t>89663.7734</t>
+  </si>
+  <si>
+    <t>36431.3906</t>
+  </si>
+  <si>
+    <t>1440x810</t>
+  </si>
+  <si>
+    <t>70285.5781</t>
+  </si>
+  <si>
+    <t>398605.344</t>
+  </si>
+  <si>
+    <t>Task 4 F4</t>
+  </si>
+  <si>
+    <t>Task 4 F0</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -155,6 +254,12 @@
       <color rgb="FF000000"/>
       <name val="Cambria"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -265,7 +370,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -285,14 +390,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -309,6 +417,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -628,24 +740,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D06E983-B581-4B51-A88B-00887F6C9E77}">
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:W38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
     <col min="2" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.42578125" customWidth="1"/>
-    <col min="12" max="12" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="12" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="33.140625" customWidth="1"/>
+    <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="21" max="22" width="11.42578125" bestFit="1" customWidth="1"/>
@@ -936,49 +1049,49 @@
       <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="9">
         <v>100</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="9">
+      <c r="C10" s="8"/>
+      <c r="D10" s="7">
         <v>250</v>
       </c>
-      <c r="E10" s="7"/>
-      <c r="F10" s="9">
+      <c r="E10" s="8"/>
+      <c r="F10" s="7">
         <v>500</v>
       </c>
-      <c r="G10" s="7"/>
-      <c r="H10" s="9">
+      <c r="G10" s="8"/>
+      <c r="H10" s="7">
         <v>750</v>
       </c>
-      <c r="I10" s="7"/>
-      <c r="J10" s="9">
+      <c r="I10" s="8"/>
+      <c r="J10" s="7">
         <v>1000</v>
       </c>
-      <c r="K10" s="7"/>
+      <c r="K10" s="8"/>
       <c r="M10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N10" s="8">
+      <c r="N10" s="9">
         <v>100</v>
       </c>
-      <c r="O10" s="7"/>
-      <c r="P10" s="9">
+      <c r="O10" s="8"/>
+      <c r="P10" s="7">
         <v>250</v>
       </c>
-      <c r="Q10" s="7"/>
-      <c r="R10" s="9">
+      <c r="Q10" s="8"/>
+      <c r="R10" s="7">
         <v>500</v>
       </c>
-      <c r="S10" s="7"/>
-      <c r="T10" s="9">
+      <c r="S10" s="8"/>
+      <c r="T10" s="7">
         <v>750</v>
       </c>
-      <c r="U10" s="7"/>
-      <c r="V10" s="9">
+      <c r="U10" s="8"/>
+      <c r="V10" s="7">
         <v>1000</v>
       </c>
-      <c r="W10" s="7"/>
+      <c r="W10" s="8"/>
     </row>
     <row r="11" spans="1:23" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
@@ -1388,7 +1501,7 @@
         <v>729987</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -1396,7 +1509,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>0</v>
       </c>
@@ -1428,7 +1541,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>7</v>
       </c>
@@ -1460,7 +1573,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>8</v>
       </c>
@@ -1492,7 +1605,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>9</v>
       </c>
@@ -1524,7 +1637,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>10</v>
       </c>
@@ -1556,7 +1669,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>11</v>
       </c>
@@ -1586,6 +1699,452 @@
       </c>
       <c r="L24" s="4" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>62</v>
+      </c>
+      <c r="H26" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="4">
+        <v>429346</v>
+      </c>
+      <c r="C28" s="4">
+        <v>1456</v>
+      </c>
+      <c r="D28" s="4">
+        <v>174784401</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F28" s="4">
+        <v>1</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I28" s="4">
+        <v>429346</v>
+      </c>
+      <c r="J28" s="4">
+        <v>21874</v>
+      </c>
+      <c r="K28" s="4">
+        <v>1049904000</v>
+      </c>
+      <c r="L28" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="M28" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" s="6">
+        <v>1715815</v>
+      </c>
+      <c r="C29" s="6">
+        <v>5826</v>
+      </c>
+      <c r="D29" s="6">
+        <v>699188342</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F29" s="6">
+        <v>4</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I29" s="6">
+        <v>1715815</v>
+      </c>
+      <c r="J29" s="6">
+        <v>87697</v>
+      </c>
+      <c r="K29" s="6">
+        <v>4209456000</v>
+      </c>
+      <c r="L29" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="M29" s="6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="4">
+        <v>2010009</v>
+      </c>
+      <c r="C30" s="4">
+        <v>6825</v>
+      </c>
+      <c r="D30" s="4">
+        <v>819109968</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F30" s="4">
+        <v>6</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I30" s="4">
+        <v>2010009</v>
+      </c>
+      <c r="J30" s="4">
+        <v>102589</v>
+      </c>
+      <c r="K30" s="4">
+        <v>635400704</v>
+      </c>
+      <c r="L30" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M30" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" s="6">
+        <v>3392211</v>
+      </c>
+      <c r="C31" s="6">
+        <v>11520</v>
+      </c>
+      <c r="D31" s="6">
+        <v>1382478626</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F31" s="6">
+        <v>12</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I31" s="6">
+        <v>3392211</v>
+      </c>
+      <c r="J31" s="6">
+        <v>173409</v>
+      </c>
+      <c r="K31" s="6">
+        <v>4028664704</v>
+      </c>
+      <c r="L31" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M31" s="6">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="4">
+        <v>6030298</v>
+      </c>
+      <c r="C32" s="4">
+        <v>20481</v>
+      </c>
+      <c r="D32" s="4">
+        <v>2457725493</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F32" s="4">
+        <v>15</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I32" s="4">
+        <v>6030298</v>
+      </c>
+      <c r="J32" s="4">
+        <v>308546</v>
+      </c>
+      <c r="K32" s="4">
+        <v>1925306112</v>
+      </c>
+      <c r="L32" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M32" s="4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="6">
+        <v>9412365</v>
+      </c>
+      <c r="C33" s="6">
+        <v>31973</v>
+      </c>
+      <c r="D33" s="6">
+        <v>3836802595</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F33" s="6">
+        <v>28</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I33" s="6">
+        <v>9412365</v>
+      </c>
+      <c r="J33" s="6">
+        <v>481697</v>
+      </c>
+      <c r="K33" s="6">
+        <v>1646619520</v>
+      </c>
+      <c r="L33" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="M33" s="6">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" s="4">
+        <v>15423595</v>
+      </c>
+      <c r="C34" s="4">
+        <v>52391</v>
+      </c>
+      <c r="D34" s="4">
+        <v>1992072046</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F34" s="4">
+        <v>40</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I34" s="4">
+        <v>15423595</v>
+      </c>
+      <c r="J34" s="4">
+        <v>789849</v>
+      </c>
+      <c r="K34" s="4">
+        <v>3553013632</v>
+      </c>
+      <c r="L34" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="M34" s="4">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="6">
+        <v>24099487</v>
+      </c>
+      <c r="C35" s="6">
+        <v>81861</v>
+      </c>
+      <c r="D35" s="6">
+        <v>1233407928</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F35" s="6">
+        <v>28</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I35" s="6">
+        <v>24099487</v>
+      </c>
+      <c r="J35" s="6">
+        <v>1234442</v>
+      </c>
+      <c r="K35" s="6">
+        <v>3418641152</v>
+      </c>
+      <c r="L35" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M35" s="6">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B36" s="4">
+        <v>37639064</v>
+      </c>
+      <c r="C36" s="4">
+        <v>103599</v>
+      </c>
+      <c r="D36" s="4">
+        <v>3841961499</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F36" s="4">
+        <v>40</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I36" s="4">
+        <v>37639064</v>
+      </c>
+      <c r="J36" s="4">
+        <v>1928018</v>
+      </c>
+      <c r="K36" s="4">
+        <v>2350550784</v>
+      </c>
+      <c r="L36" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M36" s="4">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="6">
+        <v>37639064</v>
+      </c>
+      <c r="C37" s="6">
+        <v>127862</v>
+      </c>
+      <c r="D37" s="6">
+        <v>2458541365</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F37" s="6">
+        <v>45</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I37" s="6">
+        <v>54212127</v>
+      </c>
+      <c r="J37" s="6">
+        <v>2777384</v>
+      </c>
+      <c r="K37" s="10">
+        <v>170445824</v>
+      </c>
+      <c r="L37" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="M37" s="6">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="4">
+        <v>54212127</v>
+      </c>
+      <c r="C38" s="4">
+        <v>184159</v>
+      </c>
+      <c r="D38" s="4">
+        <v>624256552</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F38" s="4">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1601,6 +2160,7 @@
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="N10:O10"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/EEE3096S SMTROS022 Pracs/Prac 3/Misc/Raw Data.xlsx
+++ b/EEE3096S SMTROS022 Pracs/Prac 3/Misc/Raw Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uctcloud-my.sharepoint.com/personal/smtros022_myuct_ac_za/Documents/Fourth Year/Sem 2/EEE3096S/EEE3096S Git Repo SMTROS022/EEE3096S SMTROS022 Pracs/Prac 3/Misc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="409" documentId="8_{C64EA8E1-BEFA-49D1-BF1E-9A3345DDF2F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC05B23D-85A6-4021-B907-02E0DCE0A662}"/>
+  <xr:revisionPtr revIDLastSave="455" documentId="8_{C64EA8E1-BEFA-49D1-BF1E-9A3345DDF2F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{108138AB-7840-4B11-A8D9-11C7150FFF91}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DB21F44C-0F24-4ECD-93E7-EFB15482C059}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DB21F44C-0F24-4ECD-93E7-EFB15482C059}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="68">
   <si>
     <t>Resolution</t>
   </si>
@@ -228,6 +228,18 @@
   </si>
   <si>
     <t>Task 4 F0</t>
+  </si>
+  <si>
+    <t>Checksum (Float)</t>
+  </si>
+  <si>
+    <t>Time (ms) (Float)</t>
+  </si>
+  <si>
+    <t>Task 5 FPU</t>
+  </si>
+  <si>
+    <t>Task 5 NO FPU</t>
   </si>
 </sst>
 </file>
@@ -740,7 +752,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D06E983-B581-4B51-A88B-00887F6C9E77}">
-  <dimension ref="A1:W38"/>
+  <dimension ref="A1:W54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
@@ -750,7 +762,7 @@
     <col min="6" max="6" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.42578125" bestFit="1" customWidth="1"/>
@@ -2147,6 +2159,292 @@
         <v>40</v>
       </c>
     </row>
+    <row r="40" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" s="4">
+        <v>429346</v>
+      </c>
+      <c r="C42" s="4">
+        <v>1456</v>
+      </c>
+      <c r="D42" s="4">
+        <v>429364</v>
+      </c>
+      <c r="E42" s="4">
+        <v>77</v>
+      </c>
+      <c r="F42" s="4">
+        <v>429384</v>
+      </c>
+      <c r="G42" s="4">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B43" s="6">
+        <v>669809</v>
+      </c>
+      <c r="C43" s="6">
+        <v>2272</v>
+      </c>
+      <c r="D43" s="6">
+        <v>669834</v>
+      </c>
+      <c r="E43" s="6">
+        <v>120</v>
+      </c>
+      <c r="F43" s="6">
+        <v>669829</v>
+      </c>
+      <c r="G43" s="6">
+        <v>4235</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B44" s="4">
+        <v>966227</v>
+      </c>
+      <c r="C44" s="4">
+        <v>3278</v>
+      </c>
+      <c r="D44" s="4">
+        <v>966071</v>
+      </c>
+      <c r="E44" s="4">
+        <v>174</v>
+      </c>
+      <c r="F44" s="4">
+        <v>966024</v>
+      </c>
+      <c r="G44" s="4">
+        <v>6093</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B45" s="6">
+        <v>1315085</v>
+      </c>
+      <c r="C45" s="6">
+        <v>4462</v>
+      </c>
+      <c r="D45" s="6">
+        <v>1315044</v>
+      </c>
+      <c r="E45" s="6">
+        <v>237</v>
+      </c>
+      <c r="F45" s="6">
+        <v>1314999</v>
+      </c>
+      <c r="G45" s="6">
+        <v>8328</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" s="4">
+        <v>1715815</v>
+      </c>
+      <c r="C46" s="4">
+        <v>5822</v>
+      </c>
+      <c r="D46" s="4">
+        <v>1715808</v>
+      </c>
+      <c r="E46" s="4">
+        <v>309</v>
+      </c>
+      <c r="F46" s="4">
+        <v>1715812</v>
+      </c>
+      <c r="G46" s="4">
+        <v>10598</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B50" s="4">
+        <v>429346</v>
+      </c>
+      <c r="C50" s="4">
+        <v>1456</v>
+      </c>
+      <c r="D50" s="4">
+        <v>429364</v>
+      </c>
+      <c r="E50" s="4">
+        <v>1608</v>
+      </c>
+      <c r="F50" s="4">
+        <v>429384</v>
+      </c>
+      <c r="G50" s="4">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B51" s="6">
+        <v>669809</v>
+      </c>
+      <c r="C51" s="6">
+        <v>2272</v>
+      </c>
+      <c r="D51" s="6">
+        <v>669834</v>
+      </c>
+      <c r="E51" s="6">
+        <v>2535</v>
+      </c>
+      <c r="F51" s="6">
+        <v>669829</v>
+      </c>
+      <c r="G51" s="6">
+        <v>4238</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B52" s="4">
+        <v>966227</v>
+      </c>
+      <c r="C52" s="4">
+        <v>3278</v>
+      </c>
+      <c r="D52" s="4">
+        <v>966071</v>
+      </c>
+      <c r="E52" s="4">
+        <v>3655</v>
+      </c>
+      <c r="F52" s="4">
+        <v>966024</v>
+      </c>
+      <c r="G52" s="4">
+        <v>6096</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B53" s="6">
+        <v>1315085</v>
+      </c>
+      <c r="C53" s="6">
+        <v>4462</v>
+      </c>
+      <c r="D53" s="6">
+        <v>1315044</v>
+      </c>
+      <c r="E53" s="6">
+        <v>4980</v>
+      </c>
+      <c r="F53" s="6">
+        <v>1314999</v>
+      </c>
+      <c r="G53" s="6">
+        <v>8334</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B54" s="4">
+        <v>1715815</v>
+      </c>
+      <c r="C54" s="4">
+        <v>5822</v>
+      </c>
+      <c r="D54" s="4">
+        <v>1715808</v>
+      </c>
+      <c r="E54" s="4">
+        <v>6443</v>
+      </c>
+      <c r="F54" s="4">
+        <v>1715812</v>
+      </c>
+      <c r="G54" s="4">
+        <v>10600</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="P10:Q10"/>

--- a/EEE3096S SMTROS022 Pracs/Prac 3/Misc/Raw Data.xlsx
+++ b/EEE3096S SMTROS022 Pracs/Prac 3/Misc/Raw Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uctcloud-my.sharepoint.com/personal/smtros022_myuct_ac_za/Documents/Fourth Year/Sem 2/EEE3096S/EEE3096S Git Repo SMTROS022/EEE3096S SMTROS022 Pracs/Prac 3/Misc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="455" documentId="8_{C64EA8E1-BEFA-49D1-BF1E-9A3345DDF2F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{108138AB-7840-4B11-A8D9-11C7150FFF91}"/>
+  <xr:revisionPtr revIDLastSave="526" documentId="8_{C64EA8E1-BEFA-49D1-BF1E-9A3345DDF2F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1E7B5FE-6F95-470D-AC14-5E0A326E1CF5}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DB21F44C-0F24-4ECD-93E7-EFB15482C059}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="71">
   <si>
     <t>Resolution</t>
   </si>
@@ -240,6 +240,15 @@
   </si>
   <si>
     <t>Task 5 NO FPU</t>
+  </si>
+  <si>
+    <t>Task 7 F4</t>
+  </si>
+  <si>
+    <t>Scale</t>
+  </si>
+  <si>
+    <t>Task 7 F0</t>
   </si>
 </sst>
 </file>
@@ -752,7 +761,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D06E983-B581-4B51-A88B-00887F6C9E77}">
-  <dimension ref="A1:W54"/>
+  <dimension ref="A1:W72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
@@ -2445,8 +2454,334 @@
         <v>10600</v>
       </c>
     </row>
+    <row r="56" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B57" s="9">
+        <v>1000</v>
+      </c>
+      <c r="C57" s="8"/>
+      <c r="D57" s="7">
+        <v>10000</v>
+      </c>
+      <c r="E57" s="8"/>
+      <c r="F57" s="7">
+        <v>1000000</v>
+      </c>
+      <c r="G57" s="8"/>
+    </row>
+    <row r="58" spans="1:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B59" s="4">
+        <v>431301</v>
+      </c>
+      <c r="C59" s="4">
+        <v>1572</v>
+      </c>
+      <c r="D59" s="4">
+        <v>429278</v>
+      </c>
+      <c r="E59" s="4">
+        <v>1573</v>
+      </c>
+      <c r="F59" s="4">
+        <v>429282</v>
+      </c>
+      <c r="G59" s="4">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B60" s="6">
+        <v>672930</v>
+      </c>
+      <c r="C60" s="6">
+        <v>2490</v>
+      </c>
+      <c r="D60" s="6">
+        <v>670751</v>
+      </c>
+      <c r="E60" s="6">
+        <v>2499</v>
+      </c>
+      <c r="F60" s="6">
+        <v>669809</v>
+      </c>
+      <c r="G60" s="6">
+        <v>2554</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B61" s="4">
+        <v>969627</v>
+      </c>
+      <c r="C61" s="4">
+        <v>3677</v>
+      </c>
+      <c r="D61" s="4">
+        <v>966561</v>
+      </c>
+      <c r="E61" s="4">
+        <v>3687</v>
+      </c>
+      <c r="F61" s="4">
+        <v>966322</v>
+      </c>
+      <c r="G61" s="4">
+        <v>3758</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B62" s="6">
+        <v>1321191</v>
+      </c>
+      <c r="C62" s="6">
+        <v>4889</v>
+      </c>
+      <c r="D62" s="6">
+        <v>1314881</v>
+      </c>
+      <c r="E62" s="6">
+        <v>4900</v>
+      </c>
+      <c r="F62" s="6">
+        <v>1315161</v>
+      </c>
+      <c r="G62" s="6">
+        <v>5014</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B63" s="4">
+        <v>1723602</v>
+      </c>
+      <c r="C63" s="4">
+        <v>6283</v>
+      </c>
+      <c r="D63" s="4">
+        <v>1716199</v>
+      </c>
+      <c r="E63" s="4">
+        <v>6289</v>
+      </c>
+      <c r="F63" s="4">
+        <v>1715788</v>
+      </c>
+      <c r="G63" s="4">
+        <v>6406</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B66" s="9">
+        <v>1000</v>
+      </c>
+      <c r="C66" s="8"/>
+      <c r="D66" s="7">
+        <v>10000</v>
+      </c>
+      <c r="E66" s="8"/>
+      <c r="F66" s="7">
+        <v>1000000</v>
+      </c>
+      <c r="G66" s="8"/>
+    </row>
+    <row r="67" spans="1:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B68" s="4">
+        <v>431301</v>
+      </c>
+      <c r="C68" s="4">
+        <v>19420</v>
+      </c>
+      <c r="D68" s="4">
+        <v>429278</v>
+      </c>
+      <c r="E68" s="4">
+        <v>21540</v>
+      </c>
+      <c r="F68" s="4">
+        <v>429282</v>
+      </c>
+      <c r="G68" s="4">
+        <v>22881</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B69" s="6">
+        <v>672930</v>
+      </c>
+      <c r="C69" s="6">
+        <v>30321</v>
+      </c>
+      <c r="D69" s="6">
+        <v>670751</v>
+      </c>
+      <c r="E69" s="6">
+        <v>33678</v>
+      </c>
+      <c r="F69" s="6">
+        <v>669809</v>
+      </c>
+      <c r="G69" s="6">
+        <v>35751</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B70" s="4">
+        <v>969627</v>
+      </c>
+      <c r="C70" s="4">
+        <v>43821</v>
+      </c>
+      <c r="D70" s="4">
+        <v>966561</v>
+      </c>
+      <c r="E70" s="4">
+        <v>48673</v>
+      </c>
+      <c r="F70" s="4">
+        <v>966322</v>
+      </c>
+      <c r="G70" s="4">
+        <v>51724</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B71" s="6">
+        <v>1321191</v>
+      </c>
+      <c r="C71" s="6">
+        <v>59544</v>
+      </c>
+      <c r="D71" s="6">
+        <v>1314881</v>
+      </c>
+      <c r="E71" s="6">
+        <v>66066</v>
+      </c>
+      <c r="F71" s="6">
+        <v>1315161</v>
+      </c>
+      <c r="G71" s="6">
+        <v>70271</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B72" s="4">
+        <v>1723602</v>
+      </c>
+      <c r="C72" s="4">
+        <v>77710</v>
+      </c>
+      <c r="D72" s="4">
+        <v>1716199</v>
+      </c>
+      <c r="E72" s="4">
+        <v>86271</v>
+      </c>
+      <c r="F72" s="4">
+        <v>1715788</v>
+      </c>
+      <c r="G72" s="4">
+        <v>91766</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="16">
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="F57:G57"/>
     <mergeCell ref="P10:Q10"/>
     <mergeCell ref="R10:S10"/>
     <mergeCell ref="T10:U10"/>

--- a/EEE3096S SMTROS022 Pracs/Prac 3/Misc/Raw Data.xlsx
+++ b/EEE3096S SMTROS022 Pracs/Prac 3/Misc/Raw Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uctcloud-my.sharepoint.com/personal/smtros022_myuct_ac_za/Documents/Fourth Year/Sem 2/EEE3096S/EEE3096S Git Repo SMTROS022/EEE3096S SMTROS022 Pracs/Prac 3/Misc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="526" documentId="8_{C64EA8E1-BEFA-49D1-BF1E-9A3345DDF2F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1E7B5FE-6F95-470D-AC14-5E0A326E1CF5}"/>
+  <xr:revisionPtr revIDLastSave="539" documentId="8_{C64EA8E1-BEFA-49D1-BF1E-9A3345DDF2F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2710EBC-2045-4236-AAF8-1A9A5BB21096}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DB21F44C-0F24-4ECD-93E7-EFB15482C059}"/>
+    <workbookView xWindow="-21504" yWindow="0" windowWidth="21600" windowHeight="11232" xr2:uid="{DB21F44C-0F24-4ECD-93E7-EFB15482C059}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -391,7 +391,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -411,17 +411,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -777,13 +774,10 @@
     <col min="12" max="12" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="33.140625" customWidth="1"/>
+    <col min="16" max="16" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.85546875" customWidth="1"/>
+    <col min="19" max="23" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1070,46 +1064,46 @@
       <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="7">
         <v>100</v>
       </c>
       <c r="C10" s="8"/>
-      <c r="D10" s="7">
+      <c r="D10" s="9">
         <v>250</v>
       </c>
       <c r="E10" s="8"/>
-      <c r="F10" s="7">
+      <c r="F10" s="9">
         <v>500</v>
       </c>
       <c r="G10" s="8"/>
-      <c r="H10" s="7">
+      <c r="H10" s="9">
         <v>750</v>
       </c>
       <c r="I10" s="8"/>
-      <c r="J10" s="7">
+      <c r="J10" s="9">
         <v>1000</v>
       </c>
       <c r="K10" s="8"/>
       <c r="M10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N10" s="9">
+      <c r="N10" s="7">
         <v>100</v>
       </c>
       <c r="O10" s="8"/>
-      <c r="P10" s="7">
+      <c r="P10" s="9">
         <v>250</v>
       </c>
       <c r="Q10" s="8"/>
-      <c r="R10" s="7">
+      <c r="R10" s="9">
         <v>500</v>
       </c>
       <c r="S10" s="8"/>
-      <c r="T10" s="7">
+      <c r="T10" s="9">
         <v>750</v>
       </c>
       <c r="U10" s="8"/>
-      <c r="V10" s="7">
+      <c r="V10" s="9">
         <v>1000</v>
       </c>
       <c r="W10" s="8"/>
@@ -2138,7 +2132,7 @@
       <c r="J37" s="6">
         <v>2777384</v>
       </c>
-      <c r="K37" s="10">
+      <c r="K37" s="6">
         <v>170445824</v>
       </c>
       <c r="L37" s="6" t="s">
@@ -2463,15 +2457,15 @@
       <c r="A57" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B57" s="9">
+      <c r="B57" s="7">
         <v>1000</v>
       </c>
       <c r="C57" s="8"/>
-      <c r="D57" s="7">
+      <c r="D57" s="9">
         <v>10000</v>
       </c>
       <c r="E57" s="8"/>
-      <c r="F57" s="7">
+      <c r="F57" s="9">
         <v>1000000</v>
       </c>
       <c r="G57" s="8"/>
@@ -2623,15 +2617,15 @@
       <c r="A66" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B66" s="9">
+      <c r="B66" s="7">
         <v>1000</v>
       </c>
       <c r="C66" s="8"/>
-      <c r="D66" s="7">
+      <c r="D66" s="9">
         <v>10000</v>
       </c>
       <c r="E66" s="8"/>
-      <c r="F66" s="7">
+      <c r="F66" s="9">
         <v>1000000</v>
       </c>
       <c r="G66" s="8"/>
@@ -2776,12 +2770,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="D57:E57"/>
-    <mergeCell ref="F57:G57"/>
     <mergeCell ref="P10:Q10"/>
     <mergeCell ref="R10:S10"/>
     <mergeCell ref="T10:U10"/>
@@ -2792,6 +2780,12 @@
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="N10:O10"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="F57:G57"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
